--- a/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ASH/adaptive/max/results.xlsx
+++ b/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ASH/adaptive/max/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -836,6 +836,43 @@
       <c r="K13" s="4" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=80,react_th=None,scale_th=3.5,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>42.01</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>90.41</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>57.41</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>85.02</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>97.62</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>36.11</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>92.94</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>36.66</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=85,react_th=None,scale_th=3.5,type=max</t>
         </is>
       </c>
     </row>
